--- a/HD_Digital_AI_downloads_by_country.xlsx
+++ b/HD_Digital_AI_downloads_by_country.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downloads by country" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Downloads by country'!$A$4:$E$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Downloads by country'!$A$4:$F$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -87,10 +87,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -467,27 +467,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Digital &amp; AI in Human Development — downloads by country</t>
+          <t>Digital &amp; AI in Human Development — downloads by country &amp; territory</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>226 publications · 2024–2026 · WB Documents geo-located downloads. Geo-located total 393,034 (OKR downloads, ~40,712 of the 433,746 grand total, are not geo-located). Source: documentos.bancomundial.org.</t>
+          <t>226 publications · 2024–2026 · WB Documents geo-located downloads, mapped to ISO3 and de-duplicated (219 countries &amp; territories). Geo-located total 386,808; OKR downloads (not geo-located) are excluded from this view. Source: documentos.bancomundial.org.</t>
         </is>
       </c>
     </row>
@@ -504,17 +505,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>ISO3</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>World Bank region</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Downloads</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Share of geo-located</t>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Share</t>
         </is>
       </c>
     </row>
@@ -529,13 +535,18 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>High-income / Rest of World</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>188736</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="F5" s="7" t="n">
         <v>0.4879319972699634</v>
       </c>
     </row>
@@ -550,13 +561,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="E6" s="8" t="n">
         <v>17303</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.04473278732601187</v>
       </c>
     </row>
@@ -571,13 +587,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="E7" s="8" t="n">
         <v>13683</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.0353741391077744</v>
       </c>
     </row>
@@ -592,13 +613,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="E8" s="8" t="n">
         <v>12380</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="F8" s="9" t="n">
         <v>0.03200554280159666</v>
       </c>
     </row>
@@ -613,13 +639,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="E9" s="8" t="n">
         <v>10363</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="F9" s="9" t="n">
         <v>0.02679106947115882</v>
       </c>
     </row>
@@ -634,13 +665,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>South Asia</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="E10" s="8" t="n">
         <v>9501</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="F10" s="9" t="n">
         <v>0.02456257367996525</v>
       </c>
     </row>
@@ -655,13 +691,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="E11" s="8" t="n">
         <v>6945</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.01795464416454675</v>
       </c>
     </row>
@@ -676,13 +717,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="E12" s="8" t="n">
         <v>6014</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.01554776529958015</v>
       </c>
     </row>
@@ -697,13 +743,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="E13" s="8" t="n">
         <v>5678</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.01467911728816364</v>
       </c>
     </row>
@@ -718,13 +769,18 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="E14" s="8" t="n">
         <v>5377</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.01390095344460301</v>
       </c>
     </row>
@@ -739,13 +795,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="E15" s="8" t="n">
         <v>5199</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.01344077681950735</v>
       </c>
     </row>
@@ -760,13 +821,18 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="E16" s="8" t="n">
         <v>5087</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="F16" s="9" t="n">
         <v>0.01315122748236851</v>
       </c>
     </row>
@@ -781,13 +847,18 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="E17" s="8" t="n">
         <v>4876</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="F17" s="9" t="n">
         <v>0.01260573721329445</v>
       </c>
     </row>
@@ -802,13 +873,18 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="E18" s="8" t="n">
         <v>4830</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="F18" s="9" t="n">
         <v>0.01248681516411243</v>
       </c>
     </row>
@@ -823,13 +899,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>High-income / Rest of World</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="E19" s="8" t="n">
         <v>4319</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="F19" s="9" t="n">
         <v>0.01116574631341648</v>
       </c>
     </row>
@@ -844,13 +925,18 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="E20" s="8" t="n">
         <v>4164</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="F20" s="9" t="n">
         <v>0.01076503071291183</v>
       </c>
     </row>
@@ -865,13 +951,18 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="E21" s="8" t="n">
         <v>3807</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="F21" s="9" t="n">
         <v>0.009842092200781784</v>
       </c>
     </row>
@@ -886,13 +977,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>South Asia</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="E22" s="8" t="n">
         <v>3546</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.009167338834770739</v>
       </c>
     </row>
@@ -907,14 +1003,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
-        <v>3516</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.00908978097660855</v>
+      <c r="E23" s="8" t="n">
+        <v>3544</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>0.009162168310893259</v>
       </c>
     </row>
     <row r="24">
@@ -928,13 +1029,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="E24" s="8" t="n">
         <v>3342</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="F24" s="9" t="n">
         <v>0.008639945399267854</v>
       </c>
     </row>
@@ -949,13 +1055,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="E25" s="8" t="n">
         <v>2719</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="F25" s="9" t="n">
         <v>0.007029327211433062</v>
       </c>
     </row>
@@ -970,13 +1081,18 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="E26" s="8" t="n">
         <v>2421</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="F26" s="9" t="n">
         <v>0.006258919153688652</v>
       </c>
     </row>
@@ -991,13 +1107,18 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="E27" s="8" t="n">
         <v>2363</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="F27" s="9" t="n">
         <v>0.006108973961241753</v>
       </c>
     </row>
@@ -1012,13 +1133,18 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="E28" s="8" t="n">
         <v>2337</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="F28" s="9" t="n">
         <v>0.006041757150834523</v>
       </c>
     </row>
@@ -1033,13 +1159,18 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="E29" s="8" t="n">
         <v>2290</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="F29" s="9" t="n">
         <v>0.00592024983971376</v>
       </c>
     </row>
@@ -1054,13 +1185,18 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="E30" s="8" t="n">
         <v>2288</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.005915079315836281</v>
       </c>
     </row>
@@ -1075,13 +1211,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="E31" s="8" t="n">
         <v>2264</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="F31" s="9" t="n">
         <v>0.005853033029306529</v>
       </c>
     </row>
@@ -1096,13 +1237,18 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="E32" s="8" t="n">
         <v>2159</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="F32" s="9" t="n">
         <v>0.005581580525738868</v>
       </c>
     </row>
@@ -1117,13 +1263,18 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>ECU</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="E33" s="8" t="n">
         <v>2074</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="F33" s="9" t="n">
         <v>0.005361833260945999</v>
       </c>
     </row>
@@ -1138,13 +1289,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="E34" s="8" t="n">
         <v>1715</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="F34" s="9" t="n">
         <v>0.004433724224938471</v>
       </c>
     </row>
@@ -1159,13 +1315,18 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="E35" s="8" t="n">
         <v>1680</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="F35" s="9" t="n">
         <v>0.004343240057082583</v>
       </c>
     </row>
@@ -1180,13 +1341,18 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="E36" s="8" t="n">
         <v>1553</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="F36" s="9" t="n">
         <v>0.00401491179086265</v>
       </c>
     </row>
@@ -1201,13 +1367,18 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="E37" s="8" t="n">
         <v>1553</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="F37" s="9" t="n">
         <v>0.00401491179086265</v>
       </c>
     </row>
@@ -1217,19 +1388,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Korea, Rep.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n">
-        <v>1519</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0.003927012884945503</v>
+      <c r="E38" s="8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0.003981303385659035</v>
       </c>
     </row>
     <row r="39">
@@ -1243,13 +1419,18 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="E39" s="8" t="n">
         <v>1405</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="F39" s="9" t="n">
         <v>0.003632293023929185</v>
       </c>
     </row>
@@ -1264,13 +1445,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>South Asia</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="E40" s="8" t="n">
         <v>1334</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="F40" s="9" t="n">
         <v>0.00344873942627867</v>
       </c>
     </row>
@@ -1280,18 +1466,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="E41" s="8" t="n">
         <v>1310</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.00338669313974892</v>
       </c>
     </row>
@@ -1306,13 +1497,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="E42" s="8" t="n">
         <v>1250</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="F42" s="9" t="n">
         <v>0.003231577423424541</v>
       </c>
     </row>
@@ -1322,19 +1518,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Venezuela, Republica Bolivariana de</t>
+          <t>Venezuela, RB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n">
-        <v>1084</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0.002802423941593762</v>
+      <c r="E43" s="8" t="n">
+        <v>1093</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>0.002825691299042419</v>
       </c>
     </row>
     <row r="44">
@@ -1348,13 +1549,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="E44" s="8" t="n">
         <v>1065</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="F44" s="9" t="n">
         <v>0.002753303964757709</v>
       </c>
     </row>
@@ -1364,19 +1570,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Russian Federation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n">
-        <v>1026</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>0.002652478749146864</v>
+      <c r="E45" s="8" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>0.002667990320779301</v>
       </c>
     </row>
     <row r="46">
@@ -1385,19 +1596,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>1025</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.002649893487208124</v>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>0.002652478749146864</v>
       </c>
     </row>
     <row r="47">
@@ -1406,18 +1622,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="n">
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
         <v>1025</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="F47" s="9" t="n">
         <v>0.002649893487208124</v>
       </c>
     </row>
@@ -1427,19 +1648,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>0.002611114558127029</v>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>0.002649893487208124</v>
       </c>
     </row>
     <row r="49">
@@ -1448,19 +1674,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
-        <v>1009</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>0.00260852929618829</v>
+      <c r="E49" s="8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>0.002611114558127029</v>
       </c>
     </row>
     <row r="50">
@@ -1474,13 +1705,18 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n">
+      <c r="E50" s="8" t="n">
         <v>990</v>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="F50" s="9" t="n">
         <v>0.002559409319352237</v>
       </c>
     </row>
@@ -1495,13 +1731,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="E51" s="8" t="n">
         <v>963</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="F51" s="9" t="n">
         <v>0.002489607247006267</v>
       </c>
     </row>
@@ -1516,13 +1757,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D52" s="8" t="n">
+      <c r="E52" s="8" t="n">
         <v>883</v>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="F52" s="9" t="n">
         <v>0.002282786291907096</v>
       </c>
     </row>
@@ -1537,13 +1783,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="E53" s="8" t="n">
         <v>841</v>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="F53" s="9" t="n">
         <v>0.002174205290480031</v>
       </c>
     </row>
@@ -1553,19 +1804,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Egypt, Arab Republic of</t>
+          <t>Egypt, Arab Rep.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D54" s="8" t="n">
-        <v>791</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>0.00204494219354305</v>
+      <c r="E54" s="8" t="n">
+        <v>807</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>0.002086306384562884</v>
       </c>
     </row>
     <row r="55">
@@ -1579,13 +1835,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D55" s="8" t="n">
+      <c r="E55" s="8" t="n">
         <v>686</v>
       </c>
-      <c r="E55" s="9" t="n">
+      <c r="F55" s="9" t="n">
         <v>0.001773489689975388</v>
       </c>
     </row>
@@ -1600,13 +1861,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>GEO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n">
+      <c r="E56" s="8" t="n">
         <v>630</v>
       </c>
-      <c r="E56" s="9" t="n">
+      <c r="F56" s="9" t="n">
         <v>0.001628715021405969</v>
       </c>
     </row>
@@ -1621,13 +1887,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D57" s="8" t="n">
+      <c r="E57" s="8" t="n">
         <v>624</v>
       </c>
-      <c r="E57" s="9" t="n">
+      <c r="F57" s="9" t="n">
         <v>0.001613203449773531</v>
       </c>
     </row>
@@ -1642,13 +1913,18 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D58" s="8" t="n">
+      <c r="E58" s="8" t="n">
         <v>623</v>
       </c>
-      <c r="E58" s="9" t="n">
+      <c r="F58" s="9" t="n">
         <v>0.001610618187834791</v>
       </c>
     </row>
@@ -1663,13 +1939,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D59" s="8" t="n">
+      <c r="E59" s="8" t="n">
         <v>617</v>
       </c>
-      <c r="E59" s="9" t="n">
+      <c r="F59" s="9" t="n">
         <v>0.001595106616202354</v>
       </c>
     </row>
@@ -1684,13 +1965,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D60" s="8" t="n">
+      <c r="E60" s="8" t="n">
         <v>596</v>
       </c>
-      <c r="E60" s="9" t="n">
+      <c r="F60" s="9" t="n">
         <v>0.001540816115488821</v>
       </c>
     </row>
@@ -1705,13 +1991,18 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
+      <c r="E61" s="8" t="n">
         <v>552</v>
       </c>
-      <c r="E61" s="9" t="n">
+      <c r="F61" s="9" t="n">
         <v>0.001427064590184278</v>
       </c>
     </row>
@@ -1726,14 +2017,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>TWN</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D62" s="8" t="n">
-        <v>523</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0.001352091993960828</v>
+      <c r="E62" s="8" t="n">
+        <v>533</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>0.001377944613348225</v>
       </c>
     </row>
     <row r="63">
@@ -1747,13 +2043,18 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="E63" s="8" t="n">
         <v>513</v>
       </c>
-      <c r="E63" s="9" t="n">
+      <c r="F63" s="9" t="n">
         <v>0.001326239374573432</v>
       </c>
     </row>
@@ -1768,13 +2069,18 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D64" s="8" t="n">
+      <c r="E64" s="8" t="n">
         <v>505</v>
       </c>
-      <c r="E64" s="9" t="n">
+      <c r="F64" s="9" t="n">
         <v>0.001305557279063515</v>
       </c>
     </row>
@@ -1789,13 +2095,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="E65" s="8" t="n">
         <v>481</v>
       </c>
-      <c r="E65" s="9" t="n">
+      <c r="F65" s="9" t="n">
         <v>0.001243510992533763</v>
       </c>
     </row>
@@ -1810,13 +2121,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D66" s="8" t="n">
+      <c r="E66" s="8" t="n">
         <v>478</v>
       </c>
-      <c r="E66" s="9" t="n">
+      <c r="F66" s="9" t="n">
         <v>0.001235755206717545</v>
       </c>
     </row>
@@ -1831,13 +2147,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>PAN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D67" s="8" t="n">
+      <c r="E67" s="8" t="n">
         <v>454</v>
       </c>
-      <c r="E67" s="9" t="n">
+      <c r="F67" s="9" t="n">
         <v>0.001173708920187793</v>
       </c>
     </row>
@@ -1852,13 +2173,18 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>AZE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D68" s="8" t="n">
+      <c r="E68" s="8" t="n">
         <v>397</v>
       </c>
-      <c r="E68" s="9" t="n">
+      <c r="F68" s="9" t="n">
         <v>0.001026348989679634</v>
       </c>
     </row>
@@ -1873,13 +2199,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D69" s="8" t="n">
+      <c r="E69" s="8" t="n">
         <v>389</v>
       </c>
-      <c r="E69" s="9" t="n">
+      <c r="F69" s="9" t="n">
         <v>0.001005666894169717</v>
       </c>
     </row>
@@ -1894,13 +2225,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D70" s="8" t="n">
+      <c r="E70" s="8" t="n">
         <v>387</v>
       </c>
-      <c r="E70" s="9" t="n">
+      <c r="F70" s="9" t="n">
         <v>0.001000496370292238</v>
       </c>
     </row>
@@ -1915,13 +2251,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>NPL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>South Asia</t>
         </is>
       </c>
-      <c r="D71" s="8" t="n">
+      <c r="E71" s="8" t="n">
         <v>380</v>
       </c>
-      <c r="E71" s="9" t="n">
+      <c r="F71" s="9" t="n">
         <v>0.0009823995367210605</v>
       </c>
     </row>
@@ -1936,13 +2277,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D72" s="8" t="n">
+      <c r="E72" s="8" t="n">
         <v>365</v>
       </c>
-      <c r="E72" s="9" t="n">
+      <c r="F72" s="9" t="n">
         <v>0.0009436206076399661</v>
       </c>
     </row>
@@ -1957,13 +2303,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D73" s="8" t="n">
+      <c r="E73" s="8" t="n">
         <v>360</v>
       </c>
-      <c r="E73" s="9" t="n">
+      <c r="F73" s="9" t="n">
         <v>0.0009306942979462679</v>
       </c>
     </row>
@@ -1978,13 +2329,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>IRQ</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D74" s="8" t="n">
+      <c r="E74" s="8" t="n">
         <v>360</v>
       </c>
-      <c r="E74" s="9" t="n">
+      <c r="F74" s="9" t="n">
         <v>0.0009306942979462679</v>
       </c>
     </row>
@@ -1999,13 +2355,18 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>LKA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>South Asia</t>
         </is>
       </c>
-      <c r="D75" s="8" t="n">
+      <c r="E75" s="8" t="n">
         <v>354</v>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="F75" s="9" t="n">
         <v>0.0009151827263138301</v>
       </c>
     </row>
@@ -2020,13 +2381,18 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D76" s="8" t="n">
+      <c r="E76" s="8" t="n">
         <v>342</v>
       </c>
-      <c r="E76" s="9" t="n">
+      <c r="F76" s="9" t="n">
         <v>0.0008841595830489545</v>
       </c>
     </row>
@@ -2036,19 +2402,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n">
-        <v>329</v>
-      </c>
-      <c r="E77" s="9" t="n">
-        <v>0.0008505511778453393</v>
+      <c r="E77" s="8" t="n">
+        <v>341</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>0.0008815743211102149</v>
       </c>
     </row>
     <row r="78">
@@ -2057,19 +2428,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D78" s="8" t="n">
-        <v>325</v>
-      </c>
-      <c r="E78" s="9" t="n">
-        <v>0.0008402101300903807</v>
+      <c r="E78" s="8" t="n">
+        <v>329</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>0.0008505511778453393</v>
       </c>
     </row>
     <row r="79">
@@ -2083,13 +2459,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D79" s="8" t="n">
+      <c r="E79" s="8" t="n">
         <v>324</v>
       </c>
-      <c r="E79" s="9" t="n">
+      <c r="F79" s="9" t="n">
         <v>0.0008376248681516411</v>
       </c>
     </row>
@@ -2104,13 +2485,18 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D80" s="8" t="n">
+      <c r="E80" s="8" t="n">
         <v>312</v>
       </c>
-      <c r="E80" s="9" t="n">
+      <c r="F80" s="9" t="n">
         <v>0.0008066017248867655</v>
       </c>
     </row>
@@ -2125,13 +2511,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n">
+      <c r="E81" s="8" t="n">
         <v>293</v>
       </c>
-      <c r="E81" s="9" t="n">
+      <c r="F81" s="9" t="n">
         <v>0.0007574817480507125</v>
       </c>
     </row>
@@ -2146,13 +2537,18 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n">
+      <c r="E82" s="8" t="n">
         <v>286</v>
       </c>
-      <c r="E82" s="9" t="n">
+      <c r="F82" s="9" t="n">
         <v>0.0007393849144795351</v>
       </c>
     </row>
@@ -2167,13 +2563,18 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n">
+      <c r="E83" s="8" t="n">
         <v>261</v>
       </c>
-      <c r="E83" s="9" t="n">
+      <c r="F83" s="9" t="n">
         <v>0.0006747533660110442</v>
       </c>
     </row>
@@ -2188,13 +2589,18 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D84" s="8" t="n">
+      <c r="E84" s="8" t="n">
         <v>260</v>
       </c>
-      <c r="E84" s="9" t="n">
+      <c r="F84" s="9" t="n">
         <v>0.0006721681040723046</v>
       </c>
     </row>
@@ -2209,13 +2615,18 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n">
+      <c r="E85" s="8" t="n">
         <v>259</v>
       </c>
-      <c r="E85" s="9" t="n">
+      <c r="F85" s="9" t="n">
         <v>0.000669582842133565</v>
       </c>
     </row>
@@ -2230,13 +2641,18 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>ZWE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D86" s="8" t="n">
+      <c r="E86" s="8" t="n">
         <v>258</v>
       </c>
-      <c r="E86" s="9" t="n">
+      <c r="F86" s="9" t="n">
         <v>0.0006669975801948254</v>
       </c>
     </row>
@@ -2251,13 +2667,18 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>DZA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D87" s="8" t="n">
+      <c r="E87" s="8" t="n">
         <v>255</v>
       </c>
-      <c r="E87" s="9" t="n">
+      <c r="F87" s="9" t="n">
         <v>0.0006592417943786065</v>
       </c>
     </row>
@@ -2272,13 +2693,18 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>GLP</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D88" s="8" t="n">
+      <c r="E88" s="8" t="n">
         <v>250</v>
       </c>
-      <c r="E88" s="9" t="n">
+      <c r="F88" s="9" t="n">
         <v>0.0006463154846849083</v>
       </c>
     </row>
@@ -2288,19 +2714,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Iran, Islamic Rep.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>IRN</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D89" s="8" t="n">
-        <v>239</v>
-      </c>
-      <c r="E89" s="9" t="n">
-        <v>0.0006178776033587723</v>
+      <c r="E89" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>0.0006204628652975119</v>
       </c>
     </row>
     <row r="90">
@@ -2309,19 +2740,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Iran, Islamic Republic of</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>LBN</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D90" s="8" t="n">
-        <v>237</v>
-      </c>
-      <c r="E90" s="9" t="n">
-        <v>0.0006127070794812931</v>
+      <c r="E90" s="8" t="n">
+        <v>239</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>0.0006178776033587723</v>
       </c>
     </row>
     <row r="91">
@@ -2335,13 +2771,18 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D91" s="8" t="n">
+      <c r="E91" s="8" t="n">
         <v>236</v>
       </c>
-      <c r="E91" s="9" t="n">
+      <c r="F91" s="9" t="n">
         <v>0.0006101218175425534</v>
       </c>
     </row>
@@ -2351,19 +2792,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="n">
-        <v>214</v>
-      </c>
-      <c r="E92" s="9" t="n">
-        <v>0.0005532460548902815</v>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>219</v>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>0.0005661723645839796</v>
       </c>
     </row>
     <row r="93">
@@ -2372,19 +2818,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lao People's Democratic Republic</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="n">
-        <v>209</v>
-      </c>
-      <c r="E93" s="9" t="n">
-        <v>0.0005403197451965833</v>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>0.0005558313168290211</v>
       </c>
     </row>
     <row r="94">
@@ -2393,19 +2844,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="n">
-        <v>205</v>
-      </c>
-      <c r="E94" s="9" t="n">
-        <v>0.0005299786974416248</v>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>214</v>
+      </c>
+      <c r="F94" s="9" t="n">
+        <v>0.0005532460548902815</v>
       </c>
     </row>
     <row r="95">
@@ -2414,19 +2870,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="n">
-        <v>202</v>
-      </c>
-      <c r="E95" s="9" t="n">
-        <v>0.0005222229116254058</v>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>205</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>0.0005299786974416248</v>
       </c>
     </row>
     <row r="96">
@@ -2440,13 +2901,18 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>MOZ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D96" s="8" t="n">
+      <c r="E96" s="8" t="n">
         <v>202</v>
       </c>
-      <c r="E96" s="9" t="n">
+      <c r="F96" s="9" t="n">
         <v>0.0005222229116254058</v>
       </c>
     </row>
@@ -2461,13 +2927,18 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D97" s="8" t="n">
+      <c r="E97" s="8" t="n">
         <v>195</v>
       </c>
-      <c r="E97" s="9" t="n">
+      <c r="F97" s="9" t="n">
         <v>0.0005041260780542285</v>
       </c>
     </row>
@@ -2482,13 +2953,18 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D98" s="8" t="n">
+      <c r="E98" s="8" t="n">
         <v>195</v>
       </c>
-      <c r="E98" s="9" t="n">
+      <c r="F98" s="9" t="n">
         <v>0.0005041260780542285</v>
       </c>
     </row>
@@ -2503,13 +2979,18 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D99" s="8" t="n">
+      <c r="E99" s="8" t="n">
         <v>193</v>
       </c>
-      <c r="E99" s="9" t="n">
+      <c r="F99" s="9" t="n">
         <v>0.0004989555541767492</v>
       </c>
     </row>
@@ -2524,13 +3005,18 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D100" s="8" t="n">
+      <c r="E100" s="8" t="n">
         <v>189</v>
       </c>
-      <c r="E100" s="9" t="n">
+      <c r="F100" s="9" t="n">
         <v>0.0004886145064217906</v>
       </c>
     </row>
@@ -2545,13 +3031,18 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>NIC</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D101" s="8" t="n">
+      <c r="E101" s="8" t="n">
         <v>187</v>
       </c>
-      <c r="E101" s="9" t="n">
+      <c r="F101" s="9" t="n">
         <v>0.0004834439825443114</v>
       </c>
     </row>
@@ -2566,13 +3057,18 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>SLE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D102" s="8" t="n">
+      <c r="E102" s="8" t="n">
         <v>170</v>
       </c>
-      <c r="E102" s="9" t="n">
+      <c r="F102" s="9" t="n">
         <v>0.0004394945295857376</v>
       </c>
     </row>
@@ -2587,13 +3083,18 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>MWI</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D103" s="8" t="n">
+      <c r="E103" s="8" t="n">
         <v>161</v>
       </c>
-      <c r="E103" s="9" t="n">
+      <c r="F103" s="9" t="n">
         <v>0.0004162271721370809</v>
       </c>
     </row>
@@ -2603,18 +3104,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Congo, Dem. Rep.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="n">
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="8" t="n">
         <v>157</v>
       </c>
-      <c r="E104" s="9" t="n">
+      <c r="F104" s="9" t="n">
         <v>0.0004058861243821224</v>
       </c>
     </row>
@@ -2624,19 +3126,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Middle East &amp; N. Africa</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="E105" s="9" t="n">
-        <v>0.0004033008624433828</v>
+          <t>JAM</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>0.0004058861243821224</v>
       </c>
     </row>
     <row r="106">
@@ -2645,18 +3152,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="n">
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Middle East &amp; N. Africa</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="n">
         <v>156</v>
       </c>
-      <c r="E106" s="9" t="n">
+      <c r="F106" s="9" t="n">
         <v>0.0004033008624433828</v>
       </c>
     </row>
@@ -2666,19 +3178,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="n">
-        <v>143</v>
-      </c>
-      <c r="E107" s="9" t="n">
-        <v>0.0003696924572397676</v>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>156</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>0.0004033008624433828</v>
       </c>
     </row>
     <row r="108">
@@ -2687,19 +3204,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D108" s="8" t="n">
-        <v>142</v>
-      </c>
-      <c r="E108" s="9" t="n">
-        <v>0.0003671071953010279</v>
+      <c r="E108" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="F108" s="9" t="n">
+        <v>0.0003696924572397676</v>
       </c>
     </row>
     <row r="109">
@@ -2708,19 +3230,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>SRB</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D109" s="8" t="n">
-        <v>141</v>
-      </c>
-      <c r="E109" s="9" t="n">
-        <v>0.0003645219333622883</v>
+      <c r="E109" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>0.0003671071953010279</v>
       </c>
     </row>
     <row r="110">
@@ -2729,19 +3256,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D110" s="8" t="n">
-        <v>130</v>
-      </c>
-      <c r="E110" s="9" t="n">
-        <v>0.0003360840520361523</v>
+      <c r="E110" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>0.0003645219333622883</v>
       </c>
     </row>
     <row r="111">
@@ -2750,19 +3282,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="E111" s="9" t="n">
-        <v>0.0003309135281586731</v>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>0.0003360840520361523</v>
       </c>
     </row>
     <row r="112">
@@ -2771,15 +3308,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="E112" s="9" t="n">
-        <v>0.0003128166945874956</v>
+          <t>Somalia</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SOM</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>0.0003309135281586731</v>
       </c>
     </row>
     <row r="113">
@@ -2788,19 +3334,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>West Bank and Gaza</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="E113" s="9" t="n">
-        <v>0.0002895493371388389</v>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>0.0003050609087712767</v>
       </c>
     </row>
     <row r="114">
@@ -2809,15 +3356,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Palestinian Territory</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>0.0002843788132613596</v>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>0.0002895493371388389</v>
       </c>
     </row>
     <row r="115">
@@ -2831,13 +3387,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D115" s="8" t="n">
+      <c r="E115" s="8" t="n">
         <v>109</v>
       </c>
-      <c r="E115" s="9" t="n">
+      <c r="F115" s="9" t="n">
         <v>0.00028179355132262</v>
       </c>
     </row>
@@ -2852,13 +3413,18 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D116" s="8" t="n">
+      <c r="E116" s="8" t="n">
         <v>108</v>
       </c>
-      <c r="E116" s="9" t="n">
+      <c r="F116" s="9" t="n">
         <v>0.0002792082893838804</v>
       </c>
     </row>
@@ -2873,13 +3439,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D117" s="8" t="n">
+      <c r="E117" s="8" t="n">
         <v>106</v>
       </c>
-      <c r="E117" s="9" t="n">
+      <c r="F117" s="9" t="n">
         <v>0.0002740377655064011</v>
       </c>
     </row>
@@ -2889,19 +3460,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Slovak Republic</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="E118" s="9" t="n">
-        <v>0.0002455998841802651</v>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>0.0002481851461190048</v>
       </c>
     </row>
     <row r="119">
@@ -2910,19 +3486,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Slovak Republic</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="E119" s="9" t="n">
-        <v>0.0002430146222415255</v>
+          <t>BFA</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>0.0002455998841802651</v>
       </c>
     </row>
     <row r="120">
@@ -2936,13 +3517,18 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D120" s="8" t="n">
+      <c r="E120" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="E120" s="9" t="n">
+      <c r="F120" s="9" t="n">
         <v>0.0002404293603027859</v>
       </c>
     </row>
@@ -2957,13 +3543,18 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D121" s="8" t="n">
+      <c r="E121" s="8" t="n">
         <v>88</v>
       </c>
-      <c r="E121" s="9" t="n">
+      <c r="F121" s="9" t="n">
         <v>0.0002275030506090877</v>
       </c>
     </row>
@@ -2978,13 +3569,18 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>MDG</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D122" s="8" t="n">
+      <c r="E122" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="E122" s="9" t="n">
+      <c r="F122" s="9" t="n">
         <v>0.0002145767409153895</v>
       </c>
     </row>
@@ -2999,13 +3595,18 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>MNG</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D123" s="8" t="n">
+      <c r="E123" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="E123" s="9" t="n">
+      <c r="F123" s="9" t="n">
         <v>0.0002016504312216914</v>
       </c>
     </row>
@@ -3020,13 +3621,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>TTO</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D124" s="8" t="n">
+      <c r="E124" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="E124" s="9" t="n">
+      <c r="F124" s="9" t="n">
         <v>0.0001990651692829518</v>
       </c>
     </row>
@@ -3041,13 +3647,18 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D125" s="8" t="n">
+      <c r="E125" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="E125" s="9" t="n">
+      <c r="F125" s="9" t="n">
         <v>0.0001964799073442121</v>
       </c>
     </row>
@@ -3062,13 +3673,18 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D126" s="8" t="n">
+      <c r="E126" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="E126" s="9" t="n">
+      <c r="F126" s="9" t="n">
         <v>0.0001964799073442121</v>
       </c>
     </row>
@@ -3083,13 +3699,18 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D127" s="8" t="n">
+      <c r="E127" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="E127" s="9" t="n">
+      <c r="F127" s="9" t="n">
         <v>0.0001809683357117743</v>
       </c>
     </row>
@@ -3104,13 +3725,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D128" s="8" t="n">
+      <c r="E128" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="E128" s="9" t="n">
+      <c r="F128" s="9" t="n">
         <v>0.0001809683357117743</v>
       </c>
     </row>
@@ -3125,13 +3751,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D129" s="8" t="n">
+      <c r="E129" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="E129" s="9" t="n">
+      <c r="F129" s="9" t="n">
         <v>0.0001783830737730347</v>
       </c>
     </row>
@@ -3146,13 +3777,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>BIH</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D130" s="8" t="n">
+      <c r="E130" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="E130" s="9" t="n">
+      <c r="F130" s="9" t="n">
         <v>0.0001732125498955554</v>
       </c>
     </row>
@@ -3167,13 +3803,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D131" s="8" t="n">
+      <c r="E131" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="E131" s="9" t="n">
+      <c r="F131" s="9" t="n">
         <v>0.0001680420260180761</v>
       </c>
     </row>
@@ -3188,13 +3829,18 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D132" s="8" t="n">
+      <c r="E132" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="E132" s="9" t="n">
+      <c r="F132" s="9" t="n">
         <v>0.0001680420260180761</v>
       </c>
     </row>
@@ -3209,13 +3855,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
           <t>Middle East &amp; N. Africa</t>
         </is>
       </c>
-      <c r="D133" s="8" t="n">
+      <c r="E133" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="E133" s="9" t="n">
+      <c r="F133" s="9" t="n">
         <v>0.0001628715021405969</v>
       </c>
     </row>
@@ -3230,13 +3881,18 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D134" s="8" t="n">
+      <c r="E134" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="E134" s="9" t="n">
+      <c r="F134" s="9" t="n">
         <v>0.0001577009782631176</v>
       </c>
     </row>
@@ -3251,13 +3907,18 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>LSO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D135" s="8" t="n">
+      <c r="E135" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="E135" s="9" t="n">
+      <c r="F135" s="9" t="n">
         <v>0.0001525304543856384</v>
       </c>
     </row>
@@ -3272,13 +3933,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D136" s="8" t="n">
+      <c r="E136" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="E136" s="9" t="n">
+      <c r="F136" s="9" t="n">
         <v>0.0001447746685694195</v>
       </c>
     </row>
@@ -3293,13 +3959,18 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>AFG</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>South Asia</t>
         </is>
       </c>
-      <c r="D137" s="8" t="n">
+      <c r="E137" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="E137" s="9" t="n">
+      <c r="F137" s="9" t="n">
         <v>0.0001447746685694195</v>
       </c>
     </row>
@@ -3309,18 +3980,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Macao SAR, China</t>
+          <t>Macao</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D138" s="8" t="n">
+      <c r="E138" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="E138" s="9" t="n">
+      <c r="F138" s="9" t="n">
         <v>0.0001421894066306798</v>
       </c>
     </row>
@@ -3335,14 +4011,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>KGZ</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D139" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="E139" s="9" t="n">
-        <v>0.0001396041446919402</v>
+      <c r="E139" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>0.0001421894066306798</v>
       </c>
     </row>
     <row r="140">
@@ -3351,19 +4032,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Syrian Arab Republic</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Middle East &amp; N. Africa</t>
-        </is>
-      </c>
-      <c r="D140" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="E140" s="9" t="n">
-        <v>0.0001370188827532005</v>
+          <t>MKD</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>0.0001396041446919402</v>
       </c>
     </row>
     <row r="141">
@@ -3372,19 +4058,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Syrian Arab Rep.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D141" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="E141" s="9" t="n">
-        <v>0.0001370188827532005</v>
+          <t>SYR</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Middle East &amp; N. Africa</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>0.0001396041446919402</v>
       </c>
     </row>
     <row r="142">
@@ -3393,18 +4084,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Middle East &amp; N. Africa</t>
-        </is>
-      </c>
-      <c r="D142" s="8" t="n">
+          <t>BRB</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="E142" s="9" t="n">
+      <c r="F142" s="9" t="n">
         <v>0.0001370188827532005</v>
       </c>
     </row>
@@ -3414,19 +4110,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>South Asia</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="E143" s="9" t="n">
-        <v>0.0001344336208144609</v>
+          <t>LBY</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Middle East &amp; N. Africa</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F143" s="9" t="n">
+        <v>0.0001370188827532005</v>
       </c>
     </row>
     <row r="144">
@@ -3435,19 +4136,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D144" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="E144" s="9" t="n">
-        <v>0.0001318483588757213</v>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="F144" s="9" t="n">
+        <v>0.0001344336208144609</v>
       </c>
     </row>
     <row r="145">
@@ -3456,19 +4162,24 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D145" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="E145" s="9" t="n">
-        <v>0.0001318483588757213</v>
+          <t>MDV</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>0.0001344336208144609</v>
       </c>
     </row>
     <row r="146">
@@ -3477,19 +4188,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Brunei Darussalam</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D146" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="E146" s="9" t="n">
-        <v>0.0001292630969369816</v>
+      <c r="E146" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>0.0001318483588757213</v>
       </c>
     </row>
     <row r="147">
@@ -3503,13 +4219,18 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>LBR</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D147" s="8" t="n">
+      <c r="E147" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="E147" s="9" t="n">
+      <c r="F147" s="9" t="n">
         <v>0.000126677834998242</v>
       </c>
     </row>
@@ -3519,19 +4240,20 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Yemen, Rep.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="E148" s="9" t="n">
-        <v>0.0001215073111207628</v>
+          <t>YEM</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="F148" s="9" t="n">
+        <v>0.000126677834998242</v>
       </c>
     </row>
     <row r="149">
@@ -3540,18 +4262,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D149" s="8" t="n">
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="E149" s="9" t="n">
+      <c r="F149" s="9" t="n">
         <v>0.0001215073111207628</v>
       </c>
     </row>
@@ -3561,18 +4288,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D150" s="8" t="n">
+      <c r="E150" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="E150" s="9" t="n">
+      <c r="F150" s="9" t="n">
         <v>0.0001215073111207628</v>
       </c>
     </row>
@@ -3582,14 +4314,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" s="8" t="n">
+          <t>XKX</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>XKX</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="E151" s="9" t="n">
+      <c r="F151" s="9" t="n">
         <v>0.0001215073111207628</v>
       </c>
     </row>
@@ -3604,13 +4345,18 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
+          <t>TJK</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
           <t>Europe &amp; Central Asia</t>
         </is>
       </c>
-      <c r="D152" s="8" t="n">
+      <c r="E152" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="E152" s="9" t="n">
+      <c r="F152" s="9" t="n">
         <v>0.0001137515253045439</v>
       </c>
     </row>
@@ -3625,13 +4371,18 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D153" s="8" t="n">
+      <c r="E153" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="E153" s="9" t="n">
+      <c r="F153" s="9" t="n">
         <v>0.0001008252156108457</v>
       </c>
     </row>
@@ -3646,13 +4397,18 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>TGO</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D154" s="8" t="n">
+      <c r="E154" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="E154" s="9" t="n">
+      <c r="F154" s="9" t="n">
         <v>9.823995367210605e-05</v>
       </c>
     </row>
@@ -3662,18 +4418,23 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Virgin Islands, British</t>
+          <t>Gambia, The</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="n">
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="E155" s="9" t="n">
+      <c r="F155" s="9" t="n">
         <v>9.565469173336643e-05</v>
       </c>
     </row>
@@ -3683,19 +4444,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Virgin Islands, British</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D156" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="E156" s="9" t="n">
-        <v>9.306942979462679e-05</v>
+          <t>VGB</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="F156" s="9" t="n">
+        <v>9.565469173336643e-05</v>
       </c>
     </row>
     <row r="157">
@@ -3704,19 +4470,24 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="E157" s="9" t="n">
-        <v>8.531364397840789e-05</v>
+          <t>BDI</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="F157" s="9" t="n">
+        <v>9.306942979462679e-05</v>
       </c>
     </row>
     <row r="158">
@@ -3725,18 +4496,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Middle East &amp; N. Africa</t>
-        </is>
-      </c>
-      <c r="D158" s="8" t="n">
+          <t>GUY</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E158" s="9" t="n">
+      <c r="F158" s="9" t="n">
         <v>8.531364397840789e-05</v>
       </c>
     </row>
@@ -3746,19 +4522,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D159" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="E159" s="9" t="n">
-        <v>8.272838203966826e-05</v>
+          <t>MLT</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Middle East &amp; N. Africa</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="F159" s="9" t="n">
+        <v>8.531364397840789e-05</v>
       </c>
     </row>
     <row r="160">
@@ -3767,18 +4548,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>South Asia</t>
-        </is>
-      </c>
-      <c r="D160" s="8" t="n">
+          <t>SYC</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="E160" s="9" t="n">
+      <c r="F160" s="9" t="n">
         <v>8.272838203966826e-05</v>
       </c>
     </row>
@@ -3788,19 +4574,24 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Gambia, The</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D161" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="E161" s="9" t="n">
-        <v>8.014312010092863e-05</v>
+          <t>BTN</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F161" s="9" t="n">
+        <v>8.272838203966826e-05</v>
       </c>
     </row>
     <row r="162">
@@ -3814,13 +4605,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
+          <t>HTI</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D162" s="8" t="n">
+      <c r="E162" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E162" s="9" t="n">
+      <c r="F162" s="9" t="n">
         <v>8.014312010092863e-05</v>
       </c>
     </row>
@@ -3835,13 +4631,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D163" s="8" t="n">
+      <c r="E163" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E163" s="9" t="n">
+      <c r="F163" s="9" t="n">
         <v>8.014312010092863e-05</v>
       </c>
     </row>
@@ -3856,13 +4657,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
+          <t>FJI</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D164" s="8" t="n">
+      <c r="E164" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E164" s="9" t="n">
+      <c r="F164" s="9" t="n">
         <v>7.755785816218899e-05</v>
       </c>
     </row>
@@ -3872,15 +4678,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="E165" s="9" t="n">
-        <v>7.238733428470973e-05</v>
+          <t>Congo, Rep.</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>COG</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="F165" s="9" t="n">
+        <v>7.497259622344936e-05</v>
       </c>
     </row>
     <row r="166">
@@ -3889,18 +4704,23 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Congo, Republic of</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D166" s="8" t="n">
+      <c r="E166" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="E166" s="9" t="n">
+      <c r="F166" s="9" t="n">
         <v>6.463154846849082e-05</v>
       </c>
     </row>
@@ -3915,13 +4735,18 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
+          <t>TCD</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D167" s="8" t="n">
+      <c r="E167" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="E167" s="9" t="n">
+      <c r="F167" s="9" t="n">
         <v>5.946102459101156e-05</v>
       </c>
     </row>
@@ -3931,18 +4756,23 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="n">
+          <t>BHS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="E168" s="9" t="n">
+      <c r="F168" s="9" t="n">
         <v>5.946102459101156e-05</v>
       </c>
     </row>
@@ -3952,19 +4782,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Bahamas, The</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D169" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="E169" s="9" t="n">
-        <v>5.946102459101156e-05</v>
+          <t>GAB</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="F169" s="9" t="n">
+        <v>5.687576265227193e-05</v>
       </c>
     </row>
     <row r="170">
@@ -3973,15 +4808,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="E170" s="9" t="n">
-        <v>5.946102459101156e-05</v>
+          <t>Djibouti</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>DJI</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Middle East &amp; N. Africa</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F170" s="9" t="n">
+        <v>5.170523877479266e-05</v>
       </c>
     </row>
     <row r="171">
@@ -3990,19 +4834,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
+          <t>SDN</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D171" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="E171" s="9" t="n">
-        <v>5.687576265227193e-05</v>
+      <c r="E171" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F171" s="9" t="n">
+        <v>5.170523877479266e-05</v>
       </c>
     </row>
     <row r="172">
@@ -4011,15 +4860,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="E172" s="9" t="n">
-        <v>5.429050071353229e-05</v>
+          <t>St. Lucia</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>LCA</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F172" s="9" t="n">
+        <v>5.170523877479266e-05</v>
       </c>
     </row>
     <row r="173">
@@ -4028,19 +4886,20 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Middle East &amp; N. Africa</t>
-        </is>
-      </c>
-      <c r="D173" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E173" s="9" t="n">
-        <v>5.170523877479266e-05</v>
+          <t>CUW</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F173" s="9" t="n">
+        <v>4.911997683605303e-05</v>
       </c>
     </row>
     <row r="174">
@@ -4049,19 +4908,24 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
+          <t>ERI</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="D174" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E174" s="9" t="n">
-        <v>5.170523877479266e-05</v>
+      <c r="E174" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F174" s="9" t="n">
+        <v>4.394945295857376e-05</v>
       </c>
     </row>
     <row r="175">
@@ -4070,15 +4934,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Curacao</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="E175" s="9" t="n">
-        <v>4.911997683605303e-05</v>
+          <t>Guinea</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>GIN</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F175" s="9" t="n">
+        <v>4.394945295857376e-05</v>
       </c>
     </row>
     <row r="176">
@@ -4087,19 +4960,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>St. Lucia</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>DMA</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D176" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="E176" s="9" t="n">
-        <v>4.911997683605303e-05</v>
+      <c r="E176" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F176" s="9" t="n">
+        <v>4.136419101983413e-05</v>
       </c>
     </row>
     <row r="177">
@@ -4108,15 +4986,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="E177" s="9" t="n">
-        <v>4.911997683605303e-05</v>
+          <t>Sao Tome and Principe</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F177" s="9" t="n">
+        <v>3.87789290810945e-05</v>
       </c>
     </row>
     <row r="178">
@@ -4125,19 +5012,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D178" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E178" s="9" t="n">
-        <v>4.394945295857376e-05</v>
+          <t>SUR</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F178" s="9" t="n">
+        <v>3.360840520361523e-05</v>
       </c>
     </row>
     <row r="179">
@@ -4146,19 +5038,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D179" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E179" s="9" t="n">
-        <v>4.394945295857376e-05</v>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F179" s="9" t="n">
+        <v>3.10231432648756e-05</v>
       </c>
     </row>
     <row r="180">
@@ -4167,19 +5064,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Congo, Democratic Republic of</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E180" s="9" t="n">
-        <v>4.394945295857376e-05</v>
+          <t>MNE</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E180" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F180" s="9" t="n">
+        <v>3.10231432648756e-05</v>
       </c>
     </row>
     <row r="181">
@@ -4188,15 +5090,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Czechia</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="E181" s="9" t="n">
-        <v>4.136419101983413e-05</v>
+          <t>Timor-Leste</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F181" s="9" t="n">
+        <v>2.843788132613596e-05</v>
       </c>
     </row>
     <row r="182">
@@ -4205,19 +5112,24 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
+          <t>GRD</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D182" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="E182" s="9" t="n">
-        <v>4.136419101983413e-05</v>
+      <c r="E182" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F182" s="9" t="n">
+        <v>2.585261938739633e-05</v>
       </c>
     </row>
     <row r="183">
@@ -4226,15 +5138,24 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="E183" s="9" t="n">
-        <v>4.136419101983413e-05</v>
+          <t>Solomon Islands</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F183" s="9" t="n">
+        <v>2.585261938739633e-05</v>
       </c>
     </row>
     <row r="184">
@@ -4243,19 +5164,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D184" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E184" s="9" t="n">
-        <v>3.87789290810945e-05</v>
+          <t>BLZ</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F184" s="9" t="n">
+        <v>2.585261938739633e-05</v>
       </c>
     </row>
     <row r="185">
@@ -4264,19 +5190,24 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D185" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="E185" s="9" t="n">
-        <v>3.360840520361523e-05</v>
+          <t>TKM</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F185" s="9" t="n">
+        <v>2.32673574486567e-05</v>
       </c>
     </row>
     <row r="186">
@@ -4285,19 +5216,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D186" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E186" s="9" t="n">
-        <v>3.10231432648756e-05</v>
+          <t>VCT</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E186" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F186" s="9" t="n">
+        <v>2.32673574486567e-05</v>
       </c>
     </row>
     <row r="187">
@@ -4306,19 +5242,24 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>St. Kitts and Nevis</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D187" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E187" s="9" t="n">
-        <v>3.10231432648756e-05</v>
+          <t>KNA</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F187" s="9" t="n">
+        <v>2.32673574486567e-05</v>
       </c>
     </row>
     <row r="188">
@@ -4327,19 +5268,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Turks and Caicos Islands</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>TCA</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D188" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E188" s="9" t="n">
-        <v>2.585261938739633e-05</v>
+      <c r="E188" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F188" s="9" t="n">
+        <v>2.32673574486567e-05</v>
       </c>
     </row>
     <row r="189">
@@ -4348,19 +5294,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Cayman Islands</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D189" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E189" s="9" t="n">
-        <v>2.585261938739633e-05</v>
+          <t>CYM</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F189" s="9" t="n">
+        <v>2.068209550991707e-05</v>
       </c>
     </row>
     <row r="190">
@@ -4369,19 +5320,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D190" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E190" s="9" t="n">
-        <v>2.585261938739633e-05</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E190" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F190" s="9" t="n">
+        <v>1.809683357117743e-05</v>
       </c>
     </row>
     <row r="191">
@@ -4390,15 +5346,24 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E191" s="9" t="n">
-        <v>2.585261938739633e-05</v>
+          <t>Central African Republic</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E191" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F191" s="9" t="n">
+        <v>1.809683357117743e-05</v>
       </c>
     </row>
     <row r="192">
@@ -4407,15 +5372,24 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Laos</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E192" s="9" t="n">
-        <v>2.585261938739633e-05</v>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>MCO</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E192" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F192" s="9" t="n">
+        <v>1.55115716324378e-05</v>
       </c>
     </row>
     <row r="193">
@@ -4424,19 +5398,24 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>New Caledonia</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D193" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E193" s="9" t="n">
-        <v>2.32673574486567e-05</v>
+          <t>NCL</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F193" s="9" t="n">
+        <v>1.55115716324378e-05</v>
       </c>
     </row>
     <row r="194">
@@ -4445,15 +5424,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E194" s="9" t="n">
-        <v>2.32673574486567e-05</v>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>PYF</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F194" s="9" t="n">
+        <v>1.292630969369817e-05</v>
       </c>
     </row>
     <row r="195">
@@ -4462,19 +5450,24 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>St. Vincent and the Grenadines</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>ABW</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D195" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E195" s="9" t="n">
-        <v>2.32673574486567e-05</v>
+      <c r="E195" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F195" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="196">
@@ -4483,19 +5476,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Turks and Caicos Islands</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
+          <t>BMU</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D196" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E196" s="9" t="n">
-        <v>2.32673574486567e-05</v>
+      <c r="E196" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F196" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="197">
@@ -4504,15 +5502,20 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Cote D'Ivoire</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E197" s="9" t="n">
-        <v>2.068209550991707e-05</v>
+          <t>Guernsey</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>GGY</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F197" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="198">
@@ -4521,15 +5524,24 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Timor Leste</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E198" s="9" t="n">
-        <v>2.068209550991707e-05</v>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F198" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="199">
@@ -4538,19 +5550,24 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>West Bank and Gaza</t>
+          <t>Mayotte</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Middle East &amp; N. Africa</t>
-        </is>
-      </c>
-      <c r="D199" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E199" s="9" t="n">
-        <v>2.068209550991707e-05</v>
+          <t>MYT</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>High-income / Rest of World</t>
+        </is>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F199" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="200">
@@ -4559,19 +5576,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>French Guiana</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
+          <t>GUF</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D200" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E200" s="9" t="n">
-        <v>2.068209550991707e-05</v>
+      <c r="E200" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F200" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="201">
@@ -4580,19 +5602,24 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Reunion</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D201" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E201" s="9" t="n">
-        <v>1.809683357117743e-05</v>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E201" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F201" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="202">
@@ -4601,19 +5628,24 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D202" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E202" s="9" t="n">
-        <v>1.809683357117743e-05</v>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>High-income / Rest of World</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F202" s="9" t="n">
+        <v>1.034104775495853e-05</v>
       </c>
     </row>
     <row r="203">
@@ -4622,19 +5654,24 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D203" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E203" s="9" t="n">
-        <v>1.55115716324378e-05</v>
+          <t>GNQ</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" s="9" t="n">
+        <v>7.7557858162189e-06</v>
       </c>
     </row>
     <row r="204">
@@ -4643,15 +5680,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Gambia</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E204" s="9" t="n">
-        <v>1.55115716324378e-05</v>
+          <t>Anguilla</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AIA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" s="9" t="n">
+        <v>7.7557858162189e-06</v>
       </c>
     </row>
     <row r="205">
@@ -4660,19 +5706,24 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>New Caledonia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D205" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E205" s="9" t="n">
-        <v>1.55115716324378e-05</v>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E205" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F205" s="9" t="n">
+        <v>7.7557858162189e-06</v>
       </c>
     </row>
     <row r="206">
@@ -4681,19 +5732,24 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>French Polynesia</t>
+          <t>Isle of Man</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D206" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E206" s="9" t="n">
-        <v>1.292630969369817e-05</v>
+          <t>IMN</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E206" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F206" s="9" t="n">
+        <v>7.7557858162189e-06</v>
       </c>
     </row>
     <row r="207">
@@ -4702,19 +5758,24 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>St. Kitts and Nevis</t>
+          <t>Martinique</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>MTQ</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
           <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
-      <c r="D207" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E207" s="9" t="n">
-        <v>1.292630969369817e-05</v>
+      <c r="E207" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F207" s="9" t="n">
+        <v>7.7557858162189e-06</v>
       </c>
     </row>
     <row r="208">
@@ -4723,15 +5784,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E208" s="9" t="n">
-        <v>1.292630969369817e-05</v>
+          <t>Vanuatu</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>VUT</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E208" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F208" s="9" t="n">
+        <v>5.170523877479266e-06</v>
       </c>
     </row>
     <row r="209">
@@ -4740,19 +5810,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Palau</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D209" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E209" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E209" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F209" s="9" t="n">
+        <v>5.170523877479266e-06</v>
       </c>
     </row>
     <row r="210">
@@ -4761,19 +5836,24 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Virgin Islands, U.S.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D210" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E210" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>VIR</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>High-income / Rest of World</t>
+        </is>
+      </c>
+      <c r="E210" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F210" s="9" t="n">
+        <v>5.170523877479266e-06</v>
       </c>
     </row>
     <row r="211">
@@ -4782,15 +5862,20 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E211" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>Sint Maarten (Dutch part)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SXM</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F211" s="9" t="n">
+        <v>5.170523877479266e-06</v>
       </c>
     </row>
     <row r="212">
@@ -4799,15 +5884,24 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Guernsey, C.I.</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E212" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>Samoa</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E212" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" s="9" t="n">
+        <v>5.170523877479266e-06</v>
       </c>
     </row>
     <row r="213">
@@ -4816,19 +5910,24 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Micronesia, Federated States of</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D213" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E213" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>FSM</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E213" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" s="9" t="n">
+        <v>5.170523877479266e-06</v>
       </c>
     </row>
     <row r="214">
@@ -4837,19 +5936,24 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mayotte</t>
+          <t>Saint Helena, Ascension and Tristan da Cunha</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
+          <t>SHN</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
           <t>High-income / Rest of World</t>
         </is>
       </c>
-      <c r="D214" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E214" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+      <c r="E214" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="215">
@@ -4858,19 +5962,24 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>French Guiana</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D215" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E215" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>GNB</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E215" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="216">
@@ -4879,19 +5988,24 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D216" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E216" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>GUM</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E216" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="217">
@@ -4900,19 +6014,24 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>High-income / Rest of World</t>
-        </is>
-      </c>
-      <c r="D217" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E217" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>KIR</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E217" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="218">
@@ -4921,15 +6040,24 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Saint Kitts and Nevis</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E218" s="9" t="n">
-        <v>1.034104775495853e-05</v>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>LIE</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E218" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="219">
@@ -4938,15 +6066,24 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E219" s="9" t="n">
-        <v>7.7557858162189e-06</v>
+          <t>Nauru</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>NRU</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>High-income / Rest of World</t>
+        </is>
+      </c>
+      <c r="E219" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="220">
@@ -4955,15 +6092,24 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Macedonia</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E220" s="9" t="n">
-        <v>7.7557858162189e-06</v>
+          <t>Tonga</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TON</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E220" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="221">
@@ -4972,19 +6118,24 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D221" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E221" s="9" t="n">
-        <v>7.7557858162189e-06</v>
+          <t>TUV</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E221" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="222">
@@ -4993,19 +6144,20 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Anguilla</t>
+          <t>Saint Martin (French part)</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D222" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E222" s="9" t="n">
-        <v>7.7557858162189e-06</v>
+          <t>MAF</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="223">
@@ -5014,563 +6166,54 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D223" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E223" s="9" t="n">
-        <v>7.7557858162189e-06</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>220</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Timor-Leste</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+          <t>MHL</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
         <is>
           <t>East Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="D224" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E224" s="9" t="n">
-        <v>7.7557858162189e-06</v>
+      <c r="E223" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" s="9" t="n">
+        <v>2.585261938739633e-06</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
-        <v>221</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Isle of Man</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D225" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E225" s="9" t="n">
-        <v>7.7557858162189e-06</v>
+      <c r="B225" s="10" t="inlineStr">
+        <is>
+          <t>All 219 countries &amp; territories</t>
+        </is>
+      </c>
+      <c r="E225" s="11" t="n">
+        <v>386808</v>
+      </c>
+      <c r="F225" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
-        <v>222</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Martinique</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="D226" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E226" s="9" t="n">
-        <v>7.7557858162189e-06</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>223</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Vanuatu</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D227" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E227" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>224</v>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Palau</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D228" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E228" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>225</v>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Cape Verde</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E229" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>226</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Virgin Islands, US</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>High-income / Rest of World</t>
-        </is>
-      </c>
-      <c r="D230" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E230" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>227</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Brunei</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E231" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>228</v>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E232" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>229</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>St Maarten</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E233" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>230</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Samoa</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D234" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E234" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>231</v>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Yemen, Republic of</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Middle East &amp; N. Africa</t>
-        </is>
-      </c>
-      <c r="D235" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E235" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>232</v>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Micronesia, Federated States of</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D236" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E236" s="9" t="n">
-        <v>5.170523877479266e-06</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>233</v>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Kyrgyzstan</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E237" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>234</v>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>St. Helena</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>High-income / Rest of World</t>
-        </is>
-      </c>
-      <c r="D238" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E238" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>235</v>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Saint Lucia</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E239" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>236</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Guinea-Bissau</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="D240" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E240" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>237</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Guam</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D241" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>238</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Kiribati</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D242" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E242" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>239</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Europe &amp; Central Asia</t>
-        </is>
-      </c>
-      <c r="D243" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E243" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>240</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Nauru</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>High-income / Rest of World</t>
-        </is>
-      </c>
-      <c r="D244" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E244" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>241</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Tonga</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D245" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E245" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>242</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>243</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Tuvalu</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D247" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E247" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>244</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Saint Martin</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>245</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Marshall Islands</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>East Asia &amp; Pacific</t>
-        </is>
-      </c>
-      <c r="D249" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E249" s="9" t="n">
-        <v>2.585261938739633e-06</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="B251" s="10" t="inlineStr">
-        <is>
-          <t>All 245 countries/territories</t>
-        </is>
-      </c>
-      <c r="D251" s="11" t="n">
-        <v>386808</v>
-      </c>
-      <c r="E251" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="B252" s="13" t="inlineStr">
+      <c r="B226" s="13" t="inlineStr">
         <is>
           <t>Unattributed (Unknown / Other)</t>
         </is>
       </c>
-      <c r="D252" s="14" t="n">
+      <c r="E226" s="14" t="n">
         <v>6226</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E249"/>
+  <autoFilter ref="A4:F223"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
